--- a/output/pdf_financials_xlsx/EQ.xlsx
+++ b/output/pdf_financials_xlsx/EQ.xlsx
@@ -470,10 +470,10 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>8.965</v>
+        <v>0.008965000000000001</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>10.421</v>
+        <v>0.010421</v>
       </c>
     </row>
     <row r="5">
@@ -482,15 +482,11 @@
           <t xml:space="preserve">  Cost of Goods Sold</t>
         </is>
       </c>
-      <c r="B5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -499,15 +495,11 @@
           <t>Gross Profit</t>
         </is>
       </c>
-      <c r="B6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B6" s="3" t="n">
+        <v>0.008965000000000001</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>0.010421</v>
       </c>
     </row>
     <row r="7">
@@ -516,15 +508,11 @@
           <t xml:space="preserve">  Selling, General, &amp; Admin. Expense</t>
         </is>
       </c>
-      <c r="B7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -533,15 +521,11 @@
           <t xml:space="preserve">  Research &amp; Development</t>
         </is>
       </c>
-      <c r="B8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -550,15 +534,11 @@
           <t xml:space="preserve">  Other Operating Expense</t>
         </is>
       </c>
-      <c r="B9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -567,15 +547,11 @@
           <t xml:space="preserve">  Total Operating Expense</t>
         </is>
       </c>
-      <c r="B10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B10" s="3" t="n">
+        <v>0.009941</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>0.013405</v>
       </c>
     </row>
     <row r="11">
@@ -584,15 +560,11 @@
           <t>Operating Income</t>
         </is>
       </c>
-      <c r="B11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B11" s="3" t="n">
+        <v>-0.000976</v>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>-0.002984</v>
       </c>
     </row>
     <row r="12">
@@ -601,15 +573,11 @@
           <t xml:space="preserve">    Interest Income</t>
         </is>
       </c>
-      <c r="B12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -619,10 +587,10 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>-0.535</v>
+        <v>0</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>-0.538</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -631,15 +599,11 @@
           <t xml:space="preserve">  Net Interest Income</t>
         </is>
       </c>
-      <c r="B14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -648,15 +612,11 @@
           <t xml:space="preserve">  Other Income (Expense)</t>
         </is>
       </c>
-      <c r="B15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -665,15 +625,11 @@
           <t>Pretax Income</t>
         </is>
       </c>
-      <c r="B16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B16" s="3" t="n">
+        <v>-0.001914</v>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>-0.003427</v>
       </c>
     </row>
     <row r="17">
@@ -682,15 +638,11 @@
           <t xml:space="preserve">  Tax Provision</t>
         </is>
       </c>
-      <c r="B17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -733,15 +685,11 @@
           <t xml:space="preserve">    Net Income (Continuing Operations)</t>
         </is>
       </c>
-      <c r="B20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B20" s="3" t="n">
+        <v>-0.001914</v>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>-0.003427</v>
       </c>
     </row>
     <row r="21">
@@ -750,15 +698,11 @@
           <t xml:space="preserve">    Net Income (Discontinued Operations)</t>
         </is>
       </c>
-      <c r="B21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -767,15 +711,11 @@
           <t xml:space="preserve">  Other Income (Minority Interest)</t>
         </is>
       </c>
-      <c r="B22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -785,10 +725,10 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>-1.914</v>
+        <v>-0.001914</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>-3.427</v>
+        <v>-0.003427</v>
       </c>
     </row>
     <row r="24">
@@ -810,15 +750,11 @@
           <t>EPS (Diluted)</t>
         </is>
       </c>
-      <c r="B25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B25" s="3" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="C25" s="3" t="n">
+        <v>-0.06</v>
       </c>
     </row>
     <row r="26">
@@ -827,15 +763,11 @@
           <t>Shares Outstanding (Diluted Average)</t>
         </is>
       </c>
-      <c r="B26" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C26" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B26" s="3" t="n">
+        <v>0.04785</v>
+      </c>
+      <c r="C26" s="3" t="n">
+        <v>0.057117</v>
       </c>
     </row>
     <row r="27">
@@ -844,15 +776,11 @@
           <t>EBIT</t>
         </is>
       </c>
-      <c r="B27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B27" s="3" t="n">
+        <v>-0.001914</v>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>-0.003427</v>
       </c>
     </row>
     <row r="28">
@@ -861,15 +789,11 @@
           <t xml:space="preserve">  Depreciation, Depletion and Amortization</t>
         </is>
       </c>
-      <c r="B28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -878,15 +802,11 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="B29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B29" s="3" t="n">
+        <v>-0.001914</v>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>-0.003427</v>
       </c>
     </row>
     <row r="30">
@@ -895,15 +815,11 @@
           <t>EBITDA Margin %</t>
         </is>
       </c>
-      <c r="B30" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C30" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B30" s="3" t="n">
+        <v>-21.34969325153374</v>
+      </c>
+      <c r="C30" s="3" t="n">
+        <v>-32.88551962383649</v>
       </c>
     </row>
     <row r="31">
@@ -912,15 +828,11 @@
           <t>Tax Rate %</t>
         </is>
       </c>
-      <c r="B31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B31" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C31" s="3" t="n">
+        <v>-0</v>
       </c>
     </row>
     <row r="32">
@@ -949,15 +861,11 @@
           <t xml:space="preserve">    Cash and Cash Equivalents</t>
         </is>
       </c>
-      <c r="B34" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C34" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C34" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -966,15 +874,11 @@
           <t xml:space="preserve">    Marketable Securities</t>
         </is>
       </c>
-      <c r="B35" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C35" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C35" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -983,15 +887,11 @@
           <t xml:space="preserve">  Cash, Cash Equivalents, Marketable Securities</t>
         </is>
       </c>
-      <c r="B36" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C36" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B36" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C36" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -1013,15 +913,11 @@
           <t xml:space="preserve">    Notes Receivable</t>
         </is>
       </c>
-      <c r="B38" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C38" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C38" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -1030,15 +926,11 @@
           <t xml:space="preserve">    Loans Receivable</t>
         </is>
       </c>
-      <c r="B39" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C39" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B39" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C39" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -1047,15 +939,11 @@
           <t xml:space="preserve">    Other Current Receivables</t>
         </is>
       </c>
-      <c r="B40" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C40" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B40" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C40" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -1064,15 +952,11 @@
           <t xml:space="preserve">  Total Receivables</t>
         </is>
       </c>
-      <c r="B41" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C41" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B41" s="3" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="C41" s="3" t="n">
+        <v>4.572</v>
       </c>
     </row>
     <row r="42">
@@ -1081,15 +965,11 @@
           <t xml:space="preserve">    Inventories, Raw Materials &amp; Components</t>
         </is>
       </c>
-      <c r="B42" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C42" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B42" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C42" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -1098,15 +978,11 @@
           <t xml:space="preserve">    Inventories, Work In Process</t>
         </is>
       </c>
-      <c r="B43" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C43" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C43" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -1115,15 +991,11 @@
           <t xml:space="preserve">    Inventories, Inventories Adjustments</t>
         </is>
       </c>
-      <c r="B44" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C44" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B44" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C44" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -1132,15 +1004,11 @@
           <t xml:space="preserve">    Inventories, Finished Goods</t>
         </is>
       </c>
-      <c r="B45" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C45" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C45" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -1149,15 +1017,11 @@
           <t xml:space="preserve">    Inventories, Other</t>
         </is>
       </c>
-      <c r="B46" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C46" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B46" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C46" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -1166,15 +1030,11 @@
           <t xml:space="preserve">  Total Inventories</t>
         </is>
       </c>
-      <c r="B47" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C47" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C47" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -1196,15 +1056,11 @@
           <t xml:space="preserve">  Total Current Assets</t>
         </is>
       </c>
-      <c r="B49" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C49" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B49" s="3" t="n">
+        <v>5.948</v>
+      </c>
+      <c r="C49" s="3" t="n">
+        <v>7.978</v>
       </c>
     </row>
     <row r="50">
@@ -1213,15 +1069,11 @@
           <t xml:space="preserve">  Investments And Advances</t>
         </is>
       </c>
-      <c r="B50" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C50" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B50" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C50" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -1230,15 +1082,11 @@
           <t xml:space="preserve">      Land And Improvements</t>
         </is>
       </c>
-      <c r="B51" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C51" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C51" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -1247,15 +1095,11 @@
           <t xml:space="preserve">      Buildings And Improvements</t>
         </is>
       </c>
-      <c r="B52" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C52" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B52" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C52" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -1264,15 +1108,11 @@
           <t xml:space="preserve">      Machinery, Furniture, Equipment</t>
         </is>
       </c>
-      <c r="B53" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C53" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C53" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -1281,15 +1121,11 @@
           <t xml:space="preserve">      Construction In Progress</t>
         </is>
       </c>
-      <c r="B54" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C54" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B54" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C54" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -1315,15 +1151,11 @@
           <t xml:space="preserve">    Gross Property, Plant and Equipment</t>
         </is>
       </c>
-      <c r="B56" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C56" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B56" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C56" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -1332,15 +1164,11 @@
           <t xml:space="preserve">    Accumulated Depreciation</t>
         </is>
       </c>
-      <c r="B57" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C57" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B57" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C57" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -1350,10 +1178,10 @@
         </is>
       </c>
       <c r="B58" s="3" t="n">
-        <v>0.102</v>
+        <v>0.248</v>
       </c>
       <c r="C58" s="3" t="n">
-        <v>0.102</v>
+        <v>0.178</v>
       </c>
     </row>
     <row r="59">
@@ -1362,15 +1190,11 @@
           <t xml:space="preserve">  Intangible Assets</t>
         </is>
       </c>
-      <c r="B59" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C59" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B59" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C59" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -1392,15 +1216,11 @@
           <t xml:space="preserve">  Other Long Term Assets</t>
         </is>
       </c>
-      <c r="B61" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C61" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B61" s="3" t="n">
+        <v>6.485</v>
+      </c>
+      <c r="C61" s="3" t="n">
+        <v>9.074</v>
       </c>
     </row>
     <row r="62">
@@ -1409,15 +1229,11 @@
           <t xml:space="preserve">  Total Long-Term Assets</t>
         </is>
       </c>
-      <c r="B62" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C62" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B62" s="3" t="n">
+        <v>7.268</v>
+      </c>
+      <c r="C62" s="3" t="n">
+        <v>9.984</v>
       </c>
     </row>
     <row r="63">
@@ -1426,15 +1242,11 @@
           <t>Total Assets</t>
         </is>
       </c>
-      <c r="B63" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C63" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B63" s="3" t="n">
+        <v>13.216</v>
+      </c>
+      <c r="C63" s="3" t="n">
+        <v>17.962</v>
       </c>
     </row>
     <row r="64">
@@ -1443,15 +1255,11 @@
           <t xml:space="preserve">    Accounts Payable</t>
         </is>
       </c>
-      <c r="B64" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C64" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B64" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C64" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -1460,15 +1268,11 @@
           <t xml:space="preserve">    Total Tax Payable</t>
         </is>
       </c>
-      <c r="B65" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C65" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B65" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C65" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -1477,15 +1281,11 @@
           <t xml:space="preserve">    Other Current Payables</t>
         </is>
       </c>
-      <c r="B66" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C66" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B66" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C66" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -1494,15 +1294,11 @@
           <t xml:space="preserve">    Current Accrued Expense</t>
         </is>
       </c>
-      <c r="B67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B67" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C67" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -1524,15 +1320,11 @@
           <t xml:space="preserve">    Short-Term Debt</t>
         </is>
       </c>
-      <c r="B69" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C69" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B69" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C69" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -1541,15 +1333,11 @@
           <t xml:space="preserve">    Short-Term Capital Lease Obligation</t>
         </is>
       </c>
-      <c r="B70" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C70" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B70" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C70" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -1558,15 +1346,11 @@
           <t xml:space="preserve">  Short-Term Debt &amp; Capital Lease Obligation</t>
         </is>
       </c>
-      <c r="B71" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C71" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B71" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C71" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="72">
@@ -1575,15 +1359,11 @@
           <t xml:space="preserve">    Current Deferred Revenue</t>
         </is>
       </c>
-      <c r="B72" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C72" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B72" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C72" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -1592,15 +1372,11 @@
           <t xml:space="preserve">    Current Deferred Taxes Liabilities</t>
         </is>
       </c>
-      <c r="B73" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C73" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B73" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C73" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -1609,15 +1385,11 @@
           <t xml:space="preserve">  Deferred Tax And Revenue</t>
         </is>
       </c>
-      <c r="B74" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C74" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B74" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C74" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -1626,15 +1398,11 @@
           <t xml:space="preserve">  Other Current Liabilities</t>
         </is>
       </c>
-      <c r="B75" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C75" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B75" s="3" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="C75" s="3" t="n">
+        <v>2.429</v>
       </c>
     </row>
     <row r="76">
@@ -1643,15 +1411,11 @@
           <t xml:space="preserve">  Total Current Liabilities</t>
         </is>
       </c>
-      <c r="B76" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C76" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B76" s="3" t="n">
+        <v>2.055</v>
+      </c>
+      <c r="C76" s="3" t="n">
+        <v>5.337</v>
       </c>
     </row>
     <row r="77">
@@ -1660,15 +1424,11 @@
           <t xml:space="preserve">    Long-Term Debt</t>
         </is>
       </c>
-      <c r="B77" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C77" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B77" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C77" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="78">
@@ -1677,15 +1437,11 @@
           <t xml:space="preserve">    Long-Term Capital Lease Obligation</t>
         </is>
       </c>
-      <c r="B78" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C78" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B78" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C78" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="79">
@@ -1694,15 +1450,11 @@
           <t xml:space="preserve">  Long-Term Debt &amp; Capital Lease Obligation</t>
         </is>
       </c>
-      <c r="B79" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C79" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B79" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C79" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="80">
@@ -1728,15 +1480,11 @@
           <t xml:space="preserve">  Pension And Retirement Benefit</t>
         </is>
       </c>
-      <c r="B81" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C81" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B81" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C81" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="82">
@@ -1745,15 +1493,11 @@
           <t xml:space="preserve">    NonCurrent Deferred Revenue</t>
         </is>
       </c>
-      <c r="B82" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C82" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B82" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C82" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -1762,15 +1506,11 @@
           <t xml:space="preserve">  NonCurrent Deferred Liabilities</t>
         </is>
       </c>
-      <c r="B83" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C83" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B83" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C83" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="84">
@@ -1779,15 +1519,11 @@
           <t xml:space="preserve">  NonCurrent Deferred Income Tax</t>
         </is>
       </c>
-      <c r="B84" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C84" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B84" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C84" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="85">
@@ -1796,15 +1532,11 @@
           <t xml:space="preserve">  Other Long-Term Liabilities</t>
         </is>
       </c>
-      <c r="B85" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C85" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B85" s="3" t="n">
+        <v>3.746</v>
+      </c>
+      <c r="C85" s="3" t="n">
+        <v>5.435</v>
       </c>
     </row>
     <row r="86">
@@ -1813,15 +1545,11 @@
           <t xml:space="preserve">  Total Long-Term Liabilities</t>
         </is>
       </c>
-      <c r="B86" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C86" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B86" s="3" t="n">
+        <v>3.746</v>
+      </c>
+      <c r="C86" s="3" t="n">
+        <v>5.435</v>
       </c>
     </row>
     <row r="87">
@@ -1830,15 +1558,11 @@
           <t>Total Liabilities</t>
         </is>
       </c>
-      <c r="B87" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C87" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B87" s="3" t="n">
+        <v>5.801</v>
+      </c>
+      <c r="C87" s="3" t="n">
+        <v>10.772</v>
       </c>
     </row>
     <row r="88">
@@ -1847,15 +1571,11 @@
           <t xml:space="preserve">  Common Stock</t>
         </is>
       </c>
-      <c r="B88" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C88" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B88" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C88" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="89">
@@ -1864,15 +1584,11 @@
           <t xml:space="preserve">  Preferred Stock</t>
         </is>
       </c>
-      <c r="B89" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C89" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B89" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C89" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="90">
@@ -1898,15 +1614,11 @@
           <t xml:space="preserve">  Accumulated other comprehensive income (loss)</t>
         </is>
       </c>
-      <c r="B91" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C91" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B91" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C91" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="92">
@@ -1915,15 +1627,11 @@
           <t xml:space="preserve">  Additional Paid-In Capital</t>
         </is>
       </c>
-      <c r="B92" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C92" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B92" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C92" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="93">
@@ -1932,15 +1640,11 @@
           <t xml:space="preserve">  Treasury Stock</t>
         </is>
       </c>
-      <c r="B93" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C93" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B93" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C93" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="94">
@@ -1962,15 +1666,11 @@
           <t xml:space="preserve">  Minority Interest</t>
         </is>
       </c>
-      <c r="B95" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C95" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B95" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C95" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="96">
@@ -1979,15 +1679,11 @@
           <t>Total Equity</t>
         </is>
       </c>
-      <c r="B96" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C96" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B96" s="3" t="n">
+        <v>3.522</v>
+      </c>
+      <c r="C96" s="3" t="n">
+        <v>4.549</v>
       </c>
     </row>
     <row r="97">
@@ -1996,15 +1692,11 @@
           <t>Equity-to-Asset</t>
         </is>
       </c>
-      <c r="B97" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C97" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B97" s="3" t="n">
+        <v>0.2664951573849879</v>
+      </c>
+      <c r="C97" s="3" t="n">
+        <v>0.2532568756263222</v>
       </c>
     </row>
     <row r="98">
@@ -2054,11 +1746,15 @@
           <t xml:space="preserve">    Change In Receivables</t>
         </is>
       </c>
-      <c r="B101" s="3" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="C101" s="3" t="n">
-        <v>4.572</v>
+      <c r="B101" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C101" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="102">
@@ -2101,11 +1797,15 @@
           <t xml:space="preserve">    Change In Payables And Accrued Expense</t>
         </is>
       </c>
-      <c r="B104" s="3" t="n">
-        <v>1.705</v>
-      </c>
-      <c r="C104" s="3" t="n">
-        <v>2.908</v>
+      <c r="B104" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C104" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="105">
@@ -2646,7 +2346,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F96"/>
+  <dimension ref="A1:F38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2787,7 +2487,11 @@
           <t>Current assets total</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>CurrentAssets</t>
+        </is>
+      </c>
       <c r="E5" s="5" t="n">
         <v>5.948</v>
       </c>
@@ -2839,7 +2543,11 @@
           <t>Right-of-use asset (note 5)</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NetPPE</t>
+        </is>
+      </c>
       <c r="E7" s="5" t="n">
         <v>0.146</v>
       </c>
@@ -2912,10 +2620,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>$</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>Non-current assets total</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>TotalNonCurrentAssets</t>
+        </is>
+      </c>
       <c r="E10" s="5" t="n">
         <v>7.268</v>
       </c>
@@ -3065,7 +2777,11 @@
           <t>Current liabilities total</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>CurrentLiabilities</t>
+        </is>
+      </c>
       <c r="E16" s="5" t="n">
         <v>2.055</v>
       </c>
@@ -3137,7 +2853,11 @@
           <t>Non-current liabilities total</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>TotalNonCurrentLiabilities</t>
+        </is>
+      </c>
       <c r="E19" s="5" t="n">
         <v>3.746</v>
       </c>
@@ -3176,1882 +2896,460 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>balance_sheet</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Non-current liabilities</t>
-        </is>
-      </c>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr">
         <is>
-          <t>$</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
+          <t>Revenue (note 6) $</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>TotalRevenue</t>
+        </is>
+      </c>
       <c r="E21" s="5" t="n">
-        <v>7.268</v>
+        <v>0.008965000000000001</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>9.984</v>
+        <v>0.010421</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>income_statement</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Current assets</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Cash $</t>
+          <t>Publishing costs</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" s="5" t="n">
-        <v>3.691</v>
+        <v>0.005015</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>3.209</v>
+        <v>0.005698</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>income_statement</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Current assets</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Accounts receivable (note 18(a))</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>ChangeInReceivables</t>
-        </is>
-      </c>
+          <t>Employee compensation and benefits</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
       <c r="E23" s="5" t="n">
-        <v>2.06</v>
+        <v>0.003026</v>
       </c>
       <c r="F23" s="5" t="n">
-        <v>4.572</v>
+        <v>0.004622</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>income_statement</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Current assets</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Other current assets (note 9(a))</t>
+          <t>Other operating costs</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" s="5" t="n">
-        <v>0.197</v>
+        <v>0.001726</v>
       </c>
       <c r="F24" s="5" t="n">
-        <v>0.197</v>
+        <v>0.002061</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>income_statement</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Current assets</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Current assets total</t>
+          <t>Depreciation of property and equipment</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" s="5" t="n">
-        <v>5.948</v>
+        <v>5.4e-05</v>
       </c>
       <c r="F25" s="5" t="n">
-        <v>7.978</v>
+        <v>7.1e-05</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>income_statement</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Non-current assets</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Property and equipment (note 10)</t>
+          <t>Depreciation of right-of-use asset (note 5)</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" s="5" t="n">
-        <v>0.102</v>
+        <v>7.6e-05</v>
       </c>
       <c r="F26" s="5" t="n">
-        <v>0.102</v>
+        <v>6.999999999999999e-05</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>income_statement</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Non-current assets</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Right-of-use asset (note 5)</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
+          <t>Amortization of intangible assets</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>AmortizationOfIntangibles</t>
+        </is>
+      </c>
       <c r="E27" s="5" t="n">
-        <v>0.146</v>
+        <v>4.4e-05</v>
       </c>
       <c r="F27" s="5" t="n">
-        <v>0.076</v>
+        <v>0.000228</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>income_statement</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Non-current assets</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Intangible asset (note 2(l), 3 &amp; 11)</t>
+          <t>Impairment of goodwill and intangible assets (note 4 and 11)</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
-      <c r="E28" s="5" t="n">
-        <v>0.537</v>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F28" s="5" t="n">
-        <v>1.096</v>
+        <v>0.000655</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>income_statement</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Non-current assets</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Goodwill (note 3 &amp; 4)</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr"/>
+          <t>Expenses total</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
       <c r="E29" s="5" t="n">
-        <v>0.535</v>
+        <v>0.009941</v>
       </c>
       <c r="F29" s="5" t="n">
-        <v>0.732</v>
+        <v>0.013405</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>income_statement</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Non-current assets</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>$</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr"/>
+          <t>Loss from operations</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>OperatingIncome</t>
+        </is>
+      </c>
       <c r="E30" s="5" t="n">
-        <v>7.268</v>
+        <v>-0.000976</v>
       </c>
       <c r="F30" s="5" t="n">
-        <v>9.984</v>
+        <v>-0.002984</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>income_statement</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Current liabilities</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Accounts payable and accrued liabilities (note 9(b) &amp; 12 (a))</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>ChangeInPayablesAndAccruedExpense</t>
-        </is>
-      </c>
-      <c r="E31" s="5" t="n">
-        <v>1.705</v>
+          <t>Transaction costs of acquisition (note 3 (b))</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F31" s="5" t="n">
-        <v>2.908</v>
+        <v>-3.2e-05</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>income_statement</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Current liabilities</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Lease liability (note 5)</t>
+          <t>Additional contingent consideration (note 3 (b))</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" s="5" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.000406</v>
       </c>
       <c r="F32" s="5" t="n">
-        <v>0.132</v>
+        <v>8.500000000000001e-05</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>income_statement</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Current liabilities</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Loans and borrowings (note 12(c))</t>
+          <t>Finance income (note 7)</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E33" s="5" t="n">
+        <v>3e-06</v>
       </c>
       <c r="F33" s="5" t="n">
-        <v>1.989</v>
+        <v>4.2e-05</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>income_statement</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Current liabilities</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Contract liabilities (note 9(c))</t>
+          <t>Finance costs (note 7)</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" s="5" t="n">
-        <v>0.024</v>
+        <v>-0.000535</v>
       </c>
       <c r="F34" s="5" t="n">
-        <v>0.08599999999999999</v>
+        <v>-0.000538</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>income_statement</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Current liabilities</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Earn-out (note 3 (a))</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr"/>
+          <t>Net loss</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E35" s="5" t="n">
-        <v>0.256</v>
+        <v>-0.001914</v>
       </c>
       <c r="F35" s="5" t="n">
-        <v>0.222</v>
+        <v>-0.003427</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>income_statement</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Current liabilities</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Current liabilities total</t>
+          <t>Total comprehensive loss $</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" s="5" t="n">
-        <v>2.055</v>
+        <v>-0.001914</v>
       </c>
       <c r="F36" s="5" t="n">
-        <v>5.337</v>
+        <v>-0.003427</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>income_statement</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Non-current liabilities</t>
+          <t>Loss per share</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Lease liability (note 5)</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr"/>
+          <t>Basic and diluted $</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E37" s="5" t="n">
-        <v>0.08799999999999999</v>
+        <v>-4e-08</v>
       </c>
       <c r="F37" s="5" t="n">
-        <v>0.018</v>
+        <v>-5.999999999999999e-08</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>income_statement</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Non-current liabilities</t>
+          <t>Loss per share</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Loans and borrowings (note 12 (b))</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr"/>
+          <t>Weighted average number of shares outstanding basic and diluted</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E38" s="5" t="n">
-        <v>1.603</v>
+        <v>48.33126</v>
       </c>
       <c r="F38" s="5" t="n">
-        <v>0.08</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>cash_flow</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Non-current liabilities</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Non-current liabilities total</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr"/>
-      <c r="E39" s="5" t="n">
-        <v>3.746</v>
-      </c>
-      <c r="F39" s="5" t="n">
-        <v>5.435</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>cash_flow</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Non-current liabilities</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Shareholders’ equity</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr"/>
-      <c r="E40" s="5" t="n">
-        <v>3.522</v>
-      </c>
-      <c r="F40" s="5" t="n">
-        <v>4.549</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>cash_flow</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Non-current liabilities</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>$</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr"/>
-      <c r="E41" s="5" t="n">
-        <v>7.268</v>
-      </c>
-      <c r="F41" s="5" t="n">
-        <v>9.984</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>cash_flow</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>“Vernon Lobo” Director “Geoffrey Rotstein” Director</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Revenue (note 6) $</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr"/>
-      <c r="E42" s="5" t="n">
-        <v>8.965</v>
-      </c>
-      <c r="F42" s="5" t="n">
-        <v>10.421</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>cash_flow</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Expenses</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Publishing costs</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr"/>
-      <c r="E43" s="5" t="n">
-        <v>5.015</v>
-      </c>
-      <c r="F43" s="5" t="n">
-        <v>5.698</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>cash_flow</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Expenses</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Employee compensation and benefits</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr"/>
-      <c r="E44" s="5" t="n">
-        <v>3.026</v>
-      </c>
-      <c r="F44" s="5" t="n">
-        <v>4.622</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>cash_flow</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Expenses</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Other operating costs</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr"/>
-      <c r="E45" s="5" t="n">
-        <v>1.726</v>
-      </c>
-      <c r="F45" s="5" t="n">
-        <v>2.061</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>cash_flow</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Expenses</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Depreciation of property and equipment</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr"/>
-      <c r="E46" s="5" t="n">
-        <v>0.054</v>
-      </c>
-      <c r="F46" s="5" t="n">
-        <v>0.07099999999999999</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>cash_flow</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Expenses</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Depreciation of right-of-use asset (note 5)</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr"/>
-      <c r="E47" s="5" t="n">
-        <v>0.076</v>
-      </c>
-      <c r="F47" s="5" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>cash_flow</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Expenses</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Amortization of intangible assets</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>AmortizationOfIntangibles</t>
-        </is>
-      </c>
-      <c r="E48" s="5" t="n">
-        <v>0.044</v>
-      </c>
-      <c r="F48" s="5" t="n">
-        <v>0.228</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>cash_flow</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>Expenses</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Impairment of goodwill and intangible assets (note 4 and 11)</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr"/>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F49" s="5" t="n">
-        <v>0.655</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>cash_flow</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Expenses</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Expenses total</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr"/>
-      <c r="E50" s="5" t="n">
-        <v>9.941000000000001</v>
-      </c>
-      <c r="F50" s="5" t="n">
-        <v>13.405</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>cash_flow</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>Expenses</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Loss from operations</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr"/>
-      <c r="E51" s="5" t="n">
-        <v>-0.976</v>
-      </c>
-      <c r="F51" s="5" t="n">
-        <v>-2.984</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>cash_flow</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>Expenses</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Transaction costs of acquisition (note 3 (b))</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr"/>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F52" s="5" t="n">
-        <v>-0.032</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>cash_flow</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>Expenses</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Additional contingent consideration (note 3 (b))</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr"/>
-      <c r="E53" s="5" t="n">
-        <v>-0.406</v>
-      </c>
-      <c r="F53" s="5" t="n">
-        <v>0.08500000000000001</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>cash_flow</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>Expenses</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Finance income (note 7)</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr"/>
-      <c r="E54" s="5" t="n">
-        <v>0.003</v>
-      </c>
-      <c r="F54" s="5" t="n">
-        <v>0.042</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>cash_flow</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>Expenses</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Finance costs (note 7)</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr"/>
-      <c r="E55" s="5" t="n">
-        <v>-0.535</v>
-      </c>
-      <c r="F55" s="5" t="n">
-        <v>-0.538</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>cash_flow</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>Expenses</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Net loss</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr"/>
-      <c r="E56" s="5" t="n">
-        <v>-1.914</v>
-      </c>
-      <c r="F56" s="5" t="n">
-        <v>-3.427</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>cash_flow</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>Expenses</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Total comprehensive loss $</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr"/>
-      <c r="E57" s="5" t="n">
-        <v>-1.914</v>
-      </c>
-      <c r="F57" s="5" t="n">
-        <v>-3.427</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>cash_flow</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>Loss per share</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Basic and diluted $</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr"/>
-      <c r="E58" s="5" t="n">
-        <v>-4e-05</v>
-      </c>
-      <c r="F58" s="5" t="n">
-        <v>-6e-05</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>cash_flow</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>Loss per share</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Weighted average number of shares outstanding basic and diluted</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr"/>
-      <c r="E59" s="5" t="n">
-        <v>48331.26</v>
-      </c>
-      <c r="F59" s="5" t="n">
-        <v>56959.951</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>cash_flow</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr"/>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Balance, January 1, 2020 54,914,426 $ 77,411 $ 2,975 $ 852 $ (2,062) $</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr"/>
-      <c r="E60" s="5" t="n">
-        <v>3.522</v>
-      </c>
-      <c r="F60" s="5" t="n">
-        <v>-75.654</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>cash_flow</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr"/>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Net loss - - - - -</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr"/>
-      <c r="E61" s="5" t="n">
-        <v>-3.427</v>
-      </c>
-      <c r="F61" s="5" t="n">
-        <v>-3.427</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>cash_flow</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr"/>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Share-based payments (note 15) - - 678 - -</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr"/>
-      <c r="E62" s="5" t="n">
-        <v>0.678</v>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>cash_flow</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>Exercise of stock options</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>(note 13 &amp; 15) 181,500 215 (97) - -</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr"/>
-      <c r="E63" s="5" t="n">
-        <v>0.118</v>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>cash_flow</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>Exercise of stock options</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Exercise of warrants (note 13 &amp; 14) 3,816,082 3,658 - - -</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr"/>
-      <c r="E64" s="5" t="n">
-        <v>3.658</v>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>cash_flow</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>Exercise of stock options</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Warrants exercised - 639 - (639) -</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr"/>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>cash_flow</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>Exercise of stock options</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Expiry of warrants (note 12 &amp; 13) - - 3 (3) -</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr"/>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>cash_flow</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>Exercise of stock options</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Balance, December 31, 2020 58,912,008 $ 81,923 $ 3,559 $ 210 $ (2,062) $</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr"/>
-      <c r="E67" s="5" t="n">
-        <v>4.549</v>
-      </c>
-      <c r="F67" s="5" t="n">
-        <v>-79.081</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>cash_flow</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr"/>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Balance, January 1, 2019 47,483,306 $ 72,555 $ 2,605 $ 271 $ (2,062) $</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr"/>
-      <c r="E68" s="5" t="n">
-        <v>-0.371</v>
-      </c>
-      <c r="F68" s="5" t="n">
-        <v>-73.73999999999999</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>cash_flow</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr"/>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Share-based payments (note 15) - - 155 - -</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr"/>
-      <c r="E69" s="5" t="n">
-        <v>0.155</v>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>cash_flow</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>Exercise of stock options</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>(note 13 &amp; 15) 21,332 4 (1) - -</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr"/>
-      <c r="E70" s="5" t="n">
-        <v>0.003</v>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>cash_flow</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>Exercise of stock options</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Warrants issued (note 12 (b), 13 &amp; - - - 257 -</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr"/>
-      <c r="E71" s="5" t="n">
-        <v>0.257</v>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>cash_flow</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>14)</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Exercise of warrants (note 13 &amp; 14) 466,198 280 - - -</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr"/>
-      <c r="E72" s="5" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>cash_flow</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>14)</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Warrants exercised - 55 - (55) -</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr"/>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>cash_flow</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>14)</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Expiry of warrants (note 12) - - 216 (216) -</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr"/>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>cash_flow</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>Proceeds from private placement -</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>(note 13) 6,943,590 4,593 - 587 -</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr"/>
-      <c r="E75" s="5" t="n">
-        <v>5.18</v>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>cash_flow</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>Proceeds from private placement -</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>Share issuance costs (note 13) - (76) - - -</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr"/>
-      <c r="E76" s="5" t="n">
-        <v>-0.076</v>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>cash_flow</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>Proceeds from private placement -</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Finders’ warrants (note 13) - - - 8 -</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr"/>
-      <c r="E77" s="5" t="n">
-        <v>0.008</v>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>cash_flow</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>Proceeds from private placement -</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Balance, December 31, 2019 54,914,426 $ 77,411 $ 2,975 $ 852 $ (2,062) $</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr"/>
-      <c r="E78" s="5" t="n">
-        <v>3.522</v>
-      </c>
-      <c r="F78" s="5" t="n">
-        <v>-75.654</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr"/>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Revenue (note 6) $</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>TotalRevenue</t>
-        </is>
-      </c>
-      <c r="E79" s="5" t="n">
-        <v>8.965</v>
-      </c>
-      <c r="F79" s="5" t="n">
-        <v>10.421</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>Expenses</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Publishing costs</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr"/>
-      <c r="E80" s="5" t="n">
-        <v>5.015</v>
-      </c>
-      <c r="F80" s="5" t="n">
-        <v>5.698</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>Expenses</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Employee compensation and benefits</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr"/>
-      <c r="E81" s="5" t="n">
-        <v>3.026</v>
-      </c>
-      <c r="F81" s="5" t="n">
-        <v>4.622</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>Expenses</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Other operating costs</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr"/>
-      <c r="E82" s="5" t="n">
-        <v>1.726</v>
-      </c>
-      <c r="F82" s="5" t="n">
-        <v>2.061</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>Expenses</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Depreciation of property and equipment</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr"/>
-      <c r="E83" s="5" t="n">
-        <v>0.054</v>
-      </c>
-      <c r="F83" s="5" t="n">
-        <v>0.07099999999999999</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>Expenses</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Depreciation of right-of-use asset (note 5)</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr"/>
-      <c r="E84" s="5" t="n">
-        <v>0.076</v>
-      </c>
-      <c r="F84" s="5" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>Expenses</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Amortization of intangible assets</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>AmortizationOfIntangibles</t>
-        </is>
-      </c>
-      <c r="E85" s="5" t="n">
-        <v>0.044</v>
-      </c>
-      <c r="F85" s="5" t="n">
-        <v>0.228</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>Expenses</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Impairment of goodwill and intangible assets (note 4 and 11)</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr"/>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F86" s="5" t="n">
-        <v>0.655</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>Expenses</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Expenses total</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr"/>
-      <c r="E87" s="5" t="n">
-        <v>9.941000000000001</v>
-      </c>
-      <c r="F87" s="5" t="n">
-        <v>13.405</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>Expenses</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Loss from operations</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr"/>
-      <c r="E88" s="5" t="n">
-        <v>-0.976</v>
-      </c>
-      <c r="F88" s="5" t="n">
-        <v>-2.984</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>Expenses</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Transaction costs of acquisition (note 3 (b))</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr"/>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F89" s="5" t="n">
-        <v>-0.032</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>Expenses</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>Additional contingent consideration (note 3 (b))</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr"/>
-      <c r="E90" s="5" t="n">
-        <v>-0.406</v>
-      </c>
-      <c r="F90" s="5" t="n">
-        <v>0.08500000000000001</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>Expenses</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>Finance income (note 7)</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr"/>
-      <c r="E91" s="5" t="n">
-        <v>0.003</v>
-      </c>
-      <c r="F91" s="5" t="n">
-        <v>0.042</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>Expenses</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Finance costs (note 7)</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>InterestExpenseNonOperating</t>
-        </is>
-      </c>
-      <c r="E92" s="5" t="n">
-        <v>-0.535</v>
-      </c>
-      <c r="F92" s="5" t="n">
-        <v>-0.538</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>Expenses</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Net loss</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
-      <c r="E93" s="5" t="n">
-        <v>-1.914</v>
-      </c>
-      <c r="F93" s="5" t="n">
-        <v>-3.427</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>Expenses</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>Total comprehensive loss $</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr"/>
-      <c r="E94" s="5" t="n">
-        <v>-1.914</v>
-      </c>
-      <c r="F94" s="5" t="n">
-        <v>-3.427</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>Loss per share</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>Basic and diluted $</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
-      <c r="E95" s="5" t="n">
-        <v>-4e-08</v>
-      </c>
-      <c r="F95" s="5" t="n">
-        <v>-5.999999999999999e-08</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>Loss per share</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>Weighted average number of shares outstanding basic and diluted</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
-      <c r="E96" s="5" t="n">
-        <v>48.33126</v>
-      </c>
-      <c r="F96" s="5" t="n">
         <v>56.959951</v>
       </c>
     </row>

--- a/output/pdf_financials_xlsx/EQ.xlsx
+++ b/output/pdf_financials_xlsx/EQ.xlsx
@@ -431,6 +431,11 @@
   </sheetPr>
   <dimension ref="A1:C135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="56" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">

--- a/output/pdf_financials_xlsx/EQ.xlsx
+++ b/output/pdf_financials_xlsx/EQ.xlsx
@@ -579,10 +579,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>3e-06</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>4.2e-05</v>
       </c>
     </row>
     <row r="13">
@@ -592,10 +592,10 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="14">
@@ -644,10 +644,10 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="18">
@@ -782,10 +782,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.001914</v>
+        <v>-0.001917</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.003427</v>
+        <v>-0.003469</v>
       </c>
     </row>
     <row r="28">
@@ -808,10 +808,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.001914</v>
+        <v>-0.001917</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.003427</v>
+        <v>-0.003469</v>
       </c>
     </row>
     <row r="30">
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>-21.34969325153374</v>
+        <v>-21.38315672058003</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>-32.88551962383649</v>
+        <v>-33.28855196238365</v>
       </c>
     </row>
     <row r="31">
@@ -3218,7 +3218,11 @@
           <t>Finance income (note 7)</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr"/>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>InterestIncomeNonOperating</t>
+        </is>
+      </c>
       <c r="E33" s="5" t="n">
         <v>3e-06</v>
       </c>

--- a/output/pdf_financials_xlsx/EQ.xlsx
+++ b/output/pdf_financials_xlsx/EQ.xlsx
@@ -867,10 +867,10 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>3.691</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>3.209</v>
       </c>
     </row>
     <row r="35">
@@ -893,10 +893,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>3.691</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>3.209</v>
       </c>
     </row>
     <row r="37">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">

--- a/output/pdf_financials_xlsx/EQ.xlsx
+++ b/output/pdf_financials_xlsx/EQ.xlsx
@@ -540,10 +540,10 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>0</v>
+        <v>0.001726</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>0</v>
+        <v>0.002061</v>
       </c>
     </row>
     <row r="10">
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>0</v>
+        <v>0.000174</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>0</v>
+        <v>0.000369</v>
       </c>
     </row>
     <row r="29">
@@ -808,10 +808,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.001917</v>
+        <v>-0.001743</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.003469</v>
+        <v>-0.0031</v>
       </c>
     </row>
     <row r="30">
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>-21.38315672058003</v>
+        <v>-19.44227551589515</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>-33.28855196238365</v>
+        <v>-29.74762498800499</v>
       </c>
     </row>
     <row r="31">
@@ -2986,7 +2986,11 @@
           <t>Other operating costs</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E24" s="5" t="n">
         <v>0.001726</v>
       </c>
@@ -3010,7 +3014,11 @@
           <t>Depreciation of property and equipment</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E25" s="5" t="n">
         <v>5.4e-05</v>
       </c>
@@ -3034,7 +3042,11 @@
           <t>Depreciation of right-of-use asset (note 5)</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E26" s="5" t="n">
         <v>7.6e-05</v>
       </c>
@@ -3060,7 +3072,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E27" s="5" t="n">
